--- a/artfynd/A 12671-2022 artfynd.xlsx
+++ b/artfynd/A 12671-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12671-2022 artfynd.xlsx
+++ b/artfynd/A 12671-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66125686</v>
+        <v>66125622</v>
       </c>
       <c r="B2" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102964</v>
+        <v>102119</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ruvande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617483.2179136787</v>
+        <v>617483</v>
       </c>
       <c r="R2" t="n">
-        <v>6598543.450194965</v>
+        <v>6598543</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -798,37 +793,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66125655</v>
+        <v>116085891</v>
       </c>
       <c r="B3" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>102966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,22 +830,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalersudd, Vadholm, Aspö, Upl</t>
+          <t>Tjyvuddsviken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617483.2179136787</v>
+        <v>617511</v>
       </c>
       <c r="R3" t="n">
-        <v>6598543.450194965</v>
+        <v>6598553</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,12 +900,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markku Kemppi</t>
+          <t>Ann-Marie Thorstenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markku Kemppi</t>
+          <t>Ann-Marie Thorstenson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1038,6 +1029,361 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66125655</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalersudd, Vadholm, Aspö, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>617483</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6598543</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markku Kemppi</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markku Kemppi</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116085896</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjyvuddsviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>617511</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6598553</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ann-Marie Thorstenson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ann-Marie Thorstenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>66125639</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalersudd, Vadholm, Aspö, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>617483</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6598543</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markku Kemppi</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markku Kemppi</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12671-2022 artfynd.xlsx
+++ b/artfynd/A 12671-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66125622</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116085891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133763938</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66125655</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116085896</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,8 +1413,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66125639</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>